--- a/all reports/Vacant_01.xlsx
+++ b/all reports/Vacant_01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5683F3E8-506A-42DB-A8D5-D00F701C6DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E69EE1-AFA6-470C-B3B3-39A2C425DC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="108">
   <si>
     <t>Gm</t>
   </si>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>Shop Bill Summary (Vacant_01)</t>
+  </si>
+  <si>
+    <t>Umair Rehman</t>
+  </si>
+  <si>
+    <t>Umer Nawaz</t>
   </si>
 </sst>
 </file>
@@ -3228,10 +3234,16 @@
       <c r="A14">
         <v>9</v>
       </c>
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -3330,7 +3342,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3358,7 +3370,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4465,7 +4477,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0900-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -4551,7 +4563,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4579,7 +4591,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5686,7 +5698,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0A00-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -5772,7 +5784,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5800,7 +5812,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6907,7 +6919,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0B00-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -6993,7 +7005,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7021,7 +7033,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8128,7 +8140,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0C00-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -8214,7 +8226,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8242,7 +8254,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9435,7 +9447,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9463,7 +9475,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10653,7 +10665,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10681,7 +10693,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11870,7 +11882,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11898,7 +11910,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13087,7 +13099,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13115,7 +13127,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14304,7 +14316,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14332,7 +14344,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18271,7 +18283,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18299,7 +18311,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19488,7 +19500,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19516,7 +19528,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20705,7 +20717,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20733,7 +20745,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21922,7 +21934,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21950,7 +21962,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23144,7 +23156,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23172,7 +23184,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23505,11 +23517,11 @@
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
-        <f>+'4'!A5</f>
+        <f>+'3'!A5</f>
         <v xml:space="preserve">Customer Name : </v>
       </c>
       <c r="U16" s="164">
-        <f>+'4'!P35</f>
+        <f>+'3'!P35</f>
         <v>0</v>
       </c>
       <c r="XFD16" t="s">
@@ -23579,11 +23591,11 @@
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
-        <f>+'3'!A5</f>
+        <f>+'4'!A5</f>
         <v xml:space="preserve">Customer Name : </v>
       </c>
       <c r="U17" s="164">
-        <f>+'3'!P35</f>
+        <f>+'4'!P35</f>
         <v>0</v>
       </c>
       <c r="XFD17" t="s">
@@ -24611,7 +24623,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24639,7 +24651,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24660,7 +24672,7 @@
       <c r="L6" s="201"/>
       <c r="M6" s="201"/>
       <c r="N6" s="203" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="O6" s="203"/>
       <c r="P6" s="203"/>
@@ -25746,7 +25758,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -25832,7 +25844,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25860,7 +25872,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26967,7 +26979,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -27053,7 +27065,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27081,7 +27093,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28188,7 +28200,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0600-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -28273,7 +28285,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28301,7 +28313,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29408,7 +29420,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -29494,7 +29506,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29522,7 +29534,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30629,7 +30641,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0700-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
@@ -30715,7 +30727,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30743,7 +30755,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31850,7 +31862,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0800-000003000000}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+            <xm:f>Sheet2!$B$6:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>N6:P6</xm:sqref>
         </x14:dataValidation>
